--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487954_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487954_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6445</v>
+        <v>0.6027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2717</v>
+        <v>0.6027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3728</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1239</v>
+        <v>0.6027</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4168</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2929</v>
+        <v>0.6027</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3673</v>
+        <v>0.6027</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2781</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0892</v>
+        <v>0.6027</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2434</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8613</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3822</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.9556</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5534</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5934</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>A. SIMON DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6027</v>
+        <v>0.1482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6027</v>
+        <v>2.8657</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2.7175</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6027</v>
+        <v>-0.1167</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.7653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6027</v>
+        <v>0.6485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6027</v>
+        <v>2.1577</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.3096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6027</v>
+        <v>1.8482</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-2.2745</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.0748</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-1.1996</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.7351</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.4992</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.2359</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SIMON DIAZ</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2325</v>
+        <v>-0.6651</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8657</v>
+        <v>3.1786</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6332</v>
+        <v>-3.8437</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1167</v>
+        <v>-2.4196</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7653</v>
+        <v>1.5847</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6485</v>
+        <v>-4.0043</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1577</v>
+        <v>2.1201</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3096</v>
+        <v>2.7914</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8482</v>
+        <v>-0.6713</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2745</v>
+        <v>-4.5397</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0748</v>
+        <v>-1.2067</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1996</v>
+        <v>-3.3329</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6508</v>
+        <v>-0.3753</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4992</v>
+        <v>-0.1486</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1516</v>
+        <v>-0.2267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6036</v>
+        <v>0.9405</v>
       </c>
       <c r="W4" t="n">
         <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5455</v>
+        <v>-1.2518</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3823</v>
+        <v>-0.9507</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9279</v>
+        <v>-0.3011</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4196</v>
+        <v>0.1239</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5847</v>
+        <v>0.4168</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.0043</v>
+        <v>-0.2929</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1201</v>
+        <v>3.3673</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7914</v>
+        <v>1.2781</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6713</v>
+        <v>2.0892</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.5397</v>
+        <v>-3.2434</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2067</v>
+        <v>-0.8613</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3329</v>
+        <v>-2.3822</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2558</v>
+        <v>0.6571</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0552</v>
+        <v>0.3709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.311</v>
+        <v>0.2861</v>
       </c>
       <c r="V5" t="n">
         <v>0.9405</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9564</v>
+        <v>-1.7919</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0468</v>
+        <v>0.2833</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9096</v>
+        <v>-2.0752</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8756</v>
+        <v>-0.3257</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7047</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1709</v>
+        <v>0.2393</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6724</v>
+        <v>0.4604</v>
       </c>
       <c r="K6" t="n">
         <v>-0.0334</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.639</v>
+        <v>0.4938</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2032</v>
+        <v>-0.7861</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6713</v>
+        <v>-0.5315</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5319</v>
+        <v>-0.2545</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4089</v>
+        <v>-0.4395</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3744</v>
+        <v>-0.177</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0345</v>
+        <v>-0.2625</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>-2.4142</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4697</v>
+        <v>-2.0687</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.226</v>
+        <v>-1.0468</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2437</v>
+        <v>-1.0219</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3257</v>
+        <v>-1.8756</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7047</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2393</v>
+        <v>-1.1709</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4604</v>
+        <v>-0.6724</v>
       </c>
       <c r="K7" t="n">
         <v>-0.0334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4938</v>
+        <v>-0.639</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7861</v>
+        <v>-1.2032</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5315</v>
+        <v>-0.6713</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2545</v>
+        <v>-0.5319</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1174</v>
+        <v>-0.5212</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6864</v>
+        <v>-0.3744</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.431</v>
+        <v>-0.1469</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4142</v>
+        <v>-0.2666</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4142</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.105</v>
+        <v>-2.7598</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8217</v>
+        <v>0.3963</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2832</v>
+        <v>-3.156</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1808</v>
+        <v>-2.5642</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0404</v>
+        <v>-0.8327</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2212</v>
+        <v>-1.7315</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8611</v>
+        <v>1.6999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9754</v>
+        <v>0.3701</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8365</v>
+        <v>1.3298</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3198</v>
+        <v>-4.2641</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9351</v>
+        <v>-1.2028</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3847</v>
+        <v>-3.0613</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5858</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2789</v>
+        <v>-0.9379</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1944</v>
+        <v>-0.5285</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.4094</v>
       </c>
       <c r="V8" t="n">
         <v>0.9405</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2234</v>
+        <v>-2.926</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0112</v>
+        <v>-2.9236</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2122</v>
+        <v>-0.0024</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5642</v>
+        <v>-2.1808</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8327</v>
+        <v>0.0404</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7315</v>
+        <v>-2.2212</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6999</v>
+        <v>-0.8611</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3701</v>
+        <v>0.9754</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3298</v>
+        <v>-1.8365</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.2641</v>
+        <v>-1.3198</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2028</v>
+        <v>-0.9351</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0613</v>
+        <v>-0.3847</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R9" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4015</v>
+        <v>-0.1</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.2963</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4655</v>
+        <v>0.1963</v>
       </c>
       <c r="V9" t="n">
         <v>0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5882</v>
+        <v>-2.928</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0053</v>
+        <v>0.4128</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5935</v>
+        <v>-3.3408</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5983000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7917</v>
+        <v>-1.1315</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8736</v>
+        <v>-0.4661</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9181</v>
+        <v>-0.6654</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1349</v>
+        <v>-4.1421</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6498</v>
+        <v>-0.8535</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4851</v>
+        <v>-3.2885</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3962</v>
@@ -1312,13 +1312,13 @@
         <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.132</v>
+        <v>-0.3358</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6839</v>
+        <v>-0.4874</v>
       </c>
       <c r="V11" t="n">
         <v>1.4737</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7731</v>
+        <v>-5.6817</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8404</v>
+        <v>-2.6367</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9327</v>
+        <v>-3.045</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4118</v>
@@ -1390,13 +1390,13 @@
         <v>0.3964</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0859</v>
+        <v>0.0055</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4992</v>
+        <v>-0.2954</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4133</v>
+        <v>0.301</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6808</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.3286</v>
+        <v>-9.6904</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.4309</v>
+        <v>-7.7365</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8977</v>
+        <v>-1.9538</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0095</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1608</v>
+        <v>-0.201</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1176</v>
+        <v>-0.1881</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0432</v>
+        <v>-0.0129</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5331</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.9531</v>
+        <v>-11.4438</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.6823</v>
+        <v>-8.173</v>
       </c>
       <c r="F14" t="n">
         <v>-3.2708</v>
@@ -1546,10 +1546,10 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3765</v>
+        <v>-0.8672</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1855</v>
+        <v>-0.6762</v>
       </c>
       <c r="U14" t="n">
         <v>-0.191</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-44.5982</v>
+        <v>-44.5984</v>
       </c>
       <c r="E15" t="n">
         <v>-16.5814</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.0168</v>
+        <v>-28.0167</v>
       </c>
       <c r="G15" t="n">
         <v>-25.8783</v>
@@ -1600,7 +1600,7 @@
         <v>4.729</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4474000000000005</v>
+        <v>-0.4474000000000014</v>
       </c>
       <c r="L15" t="n">
         <v>5.176600000000001</v>
@@ -1624,13 +1624,13 @@
         <v>13.8756</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.4692</v>
+        <v>-5.469200000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.6145</v>
+        <v>-3.6147</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8546</v>
+        <v>-1.8547</v>
       </c>
       <c r="V15" t="n">
         <v>-3.3398</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.9738</v>
+        <v>10.1859</v>
       </c>
       <c r="E16" t="n">
-        <v>8.7606</v>
+        <v>7.0288</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2133</v>
+        <v>3.1571</v>
       </c>
       <c r="G16" t="n">
         <v>4.5357</v>
@@ -1702,13 +1702,13 @@
         <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1893</v>
+        <v>1.4014</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5221</v>
+        <v>0.7903</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6672</v>
+        <v>0.611</v>
       </c>
       <c r="V16" t="n">
         <v>1.4737</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.8793</v>
+        <v>8.3887</v>
       </c>
       <c r="E17" t="n">
-        <v>5.8132</v>
+        <v>6.3225</v>
       </c>
       <c r="F17" t="n">
         <v>2.0662</v>
@@ -1780,10 +1780,10 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0917</v>
+        <v>0.601</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4368</v>
+        <v>0.0726</v>
       </c>
       <c r="U17" t="n">
         <v>0.5285</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>7.5792</v>
+        <v>7.9057</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9329</v>
+        <v>6.0347</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6464</v>
+        <v>1.871</v>
       </c>
       <c r="G18" t="n">
         <v>3.3472</v>
@@ -1858,13 +1858,13 @@
         <v>3.1716</v>
       </c>
       <c r="S18" t="n">
-        <v>0.025</v>
+        <v>0.3515</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2423</v>
+        <v>0.3442</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2174</v>
+        <v>0.0072</v>
       </c>
       <c r="V18" t="n">
         <v>3.0178</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.0851</v>
+        <v>5.4706</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1387</v>
+        <v>2.8331</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9464</v>
+        <v>2.6375</v>
       </c>
       <c r="G19" t="n">
         <v>2.6372</v>
@@ -1936,13 +1936,13 @@
         <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3468</v>
+        <v>0.7323</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.3663</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.366</v>
       </c>
       <c r="V19" t="n">
         <v>-0.674</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2702</v>
+        <v>4.2692</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8558</v>
+        <v>5.6272</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4144</v>
+        <v>-1.3579</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2277</v>
+        <v>4.1442</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9356</v>
+        <v>0.7234</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7079</v>
+        <v>3.4208</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0009</v>
+        <v>4.9905</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3185</v>
+        <v>1.0492</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3175</v>
+        <v>3.9413</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2267</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6171</v>
+        <v>-0.3258</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3904</v>
+        <v>-0.5205</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8464</v>
+        <v>0.1606</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0463</v>
+        <v>0.0331</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8001</v>
+        <v>0.1275</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7997</v>
+        <v>-2.4142</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7997</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.8337</v>
+        <v>3.5571</v>
       </c>
       <c r="E21" t="n">
-        <v>5.2197</v>
+        <v>1.1427</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.386</v>
+        <v>2.4144</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1442</v>
+        <v>1.2277</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7234</v>
+        <v>1.9356</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4208</v>
+        <v>-0.7079</v>
       </c>
       <c r="J21" t="n">
-        <v>4.9905</v>
+        <v>1.0009</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0492</v>
+        <v>1.3185</v>
       </c>
       <c r="L21" t="n">
-        <v>3.9413</v>
+        <v>-0.3175</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0.2267</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3258</v>
+        <v>0.6171</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5205</v>
+        <v>-0.3904</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3787</v>
+        <v>0.3964</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.275</v>
+        <v>1.1333</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3744</v>
+        <v>0.3332</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0994</v>
+        <v>0.8001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4142</v>
+        <v>0.7997</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6036</v>
+        <v>0.7997</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.0178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2315</v>
+        <v>2.9093</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2383</v>
+        <v>0.271</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4698</v>
+        <v>2.6383</v>
       </c>
       <c r="G22" t="n">
         <v>3.6417</v>
@@ -2170,13 +2170,13 @@
         <v>2.3787</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.765</v>
+        <v>-0.0872</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6864</v>
+        <v>-0.177</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.0898</v>
       </c>
       <c r="V22" t="n">
         <v>0.9405</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5234</v>
+        <v>2.4154</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.038</v>
+        <v>0.5732</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5614</v>
+        <v>1.8422</v>
       </c>
       <c r="G23" t="n">
         <v>0.0794</v>
@@ -2248,13 +2248,13 @@
         <v>2.5769</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8663</v>
+        <v>0.0257</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6864</v>
+        <v>-0.0752</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.18</v>
+        <v>0.1008</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5024</v>
+        <v>0.573</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8577</v>
+        <v>-0.4502</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3601</v>
+        <v>1.0231</v>
       </c>
       <c r="G24" t="n">
         <v>1.7249</v>
@@ -2326,13 +2326,13 @@
         <v>3.1716</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8985</v>
+        <v>0.9691</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0696</v>
+        <v>0.3378</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.6312</v>
       </c>
       <c r="V24" t="n">
         <v>-0.337</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5853</v>
+        <v>-0.2974</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4205</v>
+        <v>-0.2168</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1648</v>
+        <v>-0.0806</v>
       </c>
       <c r="G25" t="n">
         <v>-0.358</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1186</v>
+        <v>0.4065</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3681</v>
+        <v>0.4524</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9405</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6949</v>
+        <v>-0.7792</v>
       </c>
       <c r="E26" t="n">
         <v>-1.1494</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4544</v>
+        <v>0.3702</v>
       </c>
       <c r="G26" t="n">
         <v>0.0404</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1406</v>
+        <v>-0.2249</v>
       </c>
       <c r="T26" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>44.59840000000001</v>
+        <v>44.59829999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>28.017</v>
+        <v>28.0168</v>
       </c>
       <c r="F27" t="n">
-        <v>16.5816</v>
+        <v>16.5815</v>
       </c>
       <c r="G27" t="n">
         <v>25.8784</v>
@@ -2560,13 +2560,13 @@
         <v>23.7869</v>
       </c>
       <c r="S27" t="n">
-        <v>5.469399999999999</v>
+        <v>5.4693</v>
       </c>
       <c r="T27" t="n">
         <v>1.8546</v>
       </c>
       <c r="U27" t="n">
-        <v>3.6145</v>
+        <v>3.614399999999999</v>
       </c>
       <c r="V27" t="n">
         <v>3.339700000000001</v>
